--- a/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R84"/>
+  <dimension ref="A1:R85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,16 +621,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -690,17 +690,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,7 +709,12 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -723,12 +728,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -748,7 +753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -763,7 +768,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -773,17 +778,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -792,11 +797,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -806,12 +816,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -831,7 +841,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -846,7 +856,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -856,17 +866,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>zhuxinlei</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>朱鑫磊</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -884,7 +894,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -894,12 +904,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>zhuxinlei</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>朱鑫磊</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -919,7 +929,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -934,7 +944,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -944,17 +954,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -963,16 +973,11 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -982,12 +987,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1007,7 +1012,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1022,7 +1027,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1032,17 +1037,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1051,16 +1056,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8,9,10,11,14,22</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1070,12 +1075,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1095,7 +1100,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1120,17 +1125,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1153,12 +1158,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1178,7 +1183,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1193,7 +1198,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1203,17 +1208,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1222,11 +1227,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1236,12 +1246,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1261,7 +1271,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1276,7 +1286,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1286,17 +1296,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1305,11 +1315,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1319,12 +1334,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1344,7 +1359,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1359,7 +1374,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1369,17 +1384,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1392,7 +1407,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1402,12 +1417,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1427,7 +1442,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1452,17 +1467,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1471,11 +1486,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1490,12 +1505,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1515,7 +1530,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1530,7 +1545,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1540,17 +1555,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>fanduo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>范夺</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1568,7 +1583,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1578,12 +1593,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>fanduo</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>范夺</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1603,7 +1618,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1618,7 +1633,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1628,17 +1643,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1647,16 +1662,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1666,12 +1681,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1691,7 +1706,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1706,7 +1721,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1716,17 +1731,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1744,7 +1759,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1754,12 +1769,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1779,7 +1794,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1809,12 +1824,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1823,7 +1838,12 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1837,12 +1857,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1862,7 +1882,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1877,7 +1897,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1887,17 +1907,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1915,7 +1935,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1925,12 +1945,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1950,7 +1970,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1975,17 +1995,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2008,12 +2028,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2033,7 +2053,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2048,7 +2068,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2058,17 +2078,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2077,11 +2097,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2091,12 +2116,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2116,7 +2141,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2131,7 +2156,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2141,17 +2166,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2169,7 +2194,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2179,12 +2204,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2204,7 +2229,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2219,7 +2244,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2229,17 +2254,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>caoyumiao</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>曹钰淼</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2252,12 +2277,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>22,23</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2267,12 +2292,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>caoyumiao</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>曹钰淼</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2292,7 +2317,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2307,7 +2332,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2317,17 +2342,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2340,7 +2365,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2350,12 +2375,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2375,7 +2400,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2390,7 +2415,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2400,17 +2425,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2419,11 +2444,16 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2433,12 +2463,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2458,7 +2488,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2483,17 +2513,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2521,12 +2551,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2546,7 +2576,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2561,7 +2591,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2571,17 +2601,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>caoyumiao</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>曹钰淼</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2590,16 +2620,16 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2609,12 +2639,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>caoyumiao</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>曹钰淼</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2634,7 +2664,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2649,7 +2679,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2659,17 +2689,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2678,11 +2708,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6,21</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2692,12 +2727,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2717,7 +2752,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2732,7 +2767,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2742,17 +2777,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2761,16 +2796,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2780,12 +2810,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2805,7 +2835,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2820,7 +2850,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2830,17 +2860,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2858,7 +2888,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2868,12 +2898,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2893,7 +2923,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2908,7 +2938,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2918,17 +2948,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2937,16 +2967,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2956,12 +2981,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2981,7 +3006,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2996,7 +3021,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3006,17 +3031,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>yanliumeng</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>闫刘梦</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3025,16 +3050,16 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3044,12 +3069,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>yanliumeng</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>闫刘梦</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3069,7 +3094,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3084,7 +3109,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3094,17 +3119,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>jiangmingyang</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>蒋明阳</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3113,16 +3138,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3132,12 +3152,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>jiangmingyang</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>蒋明阳</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3157,7 +3177,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3182,17 +3202,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3201,11 +3221,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8,9,10</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3220,12 +3240,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3245,7 +3265,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3260,7 +3280,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3270,17 +3290,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3289,16 +3309,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3308,12 +3323,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3333,7 +3348,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3348,7 +3363,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3358,17 +3373,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3381,12 +3396,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3396,12 +3411,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3421,7 +3436,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3436,7 +3451,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3446,17 +3461,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3465,11 +3480,16 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3479,12 +3499,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3504,7 +3524,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3519,7 +3539,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3529,17 +3549,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3557,7 +3577,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3567,12 +3587,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3592,7 +3612,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3617,17 +3637,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3636,12 +3656,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3655,12 +3670,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3680,7 +3695,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3710,12 +3725,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3724,12 +3739,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3743,12 +3753,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3768,7 +3778,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3783,7 +3793,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3793,17 +3803,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3812,16 +3822,16 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3831,12 +3841,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3856,7 +3866,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3871,7 +3881,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3881,17 +3891,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3900,16 +3910,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3919,12 +3924,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3944,7 +3949,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3959,7 +3964,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3969,17 +3974,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3988,16 +3993,16 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>13,14,15,16,17,18</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4007,12 +4012,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4032,7 +4037,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4047,7 +4052,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4057,17 +4062,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4076,11 +4081,16 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6,7,8</t>
+        </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4090,12 +4100,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4115,7 +4125,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4130,7 +4140,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4140,17 +4150,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4159,16 +4169,16 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.7222222222222222</v>
+        <v>0</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6,7,8,9,10</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4178,12 +4188,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4203,7 +4213,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4218,7 +4228,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4228,17 +4238,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>yanliumeng</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>闫刘梦</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4247,16 +4257,16 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4266,12 +4276,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>yanliumeng</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>闫刘梦</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4291,7 +4301,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4306,7 +4316,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4316,17 +4326,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4335,16 +4345,16 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4354,12 +4364,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4379,7 +4389,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4394,7 +4404,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4404,17 +4414,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4432,7 +4442,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4442,12 +4452,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4467,7 +4477,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4482,7 +4492,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4492,17 +4502,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4511,11 +4521,16 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4525,12 +4540,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4550,7 +4565,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4565,7 +4580,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4575,17 +4590,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>lvyixuan</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>吕怡萱</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4594,16 +4609,11 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4613,12 +4623,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>lvyixuan</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>吕怡萱</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4638,7 +4648,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4653,7 +4663,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4663,17 +4673,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4682,11 +4692,16 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4696,12 +4711,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4721,7 +4736,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4736,7 +4751,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4746,17 +4761,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4765,16 +4780,11 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4784,12 +4794,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4809,7 +4819,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4824,7 +4834,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4834,17 +4844,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4862,7 +4872,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4872,12 +4882,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4897,7 +4907,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4922,17 +4932,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4941,11 +4951,11 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6,7,8</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4960,12 +4970,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4985,7 +4995,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5010,17 +5020,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5029,12 +5039,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -5048,12 +5053,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5073,7 +5078,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5088,7 +5093,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5098,17 +5103,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>liangxiuzhi</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>梁秀枝</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5126,7 +5131,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5136,12 +5141,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>liangxiuzhi</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>梁秀枝</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5161,7 +5166,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5176,7 +5181,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5186,17 +5191,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5205,16 +5210,16 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5224,12 +5229,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5249,7 +5254,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5264,7 +5269,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5274,17 +5279,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5302,7 +5307,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5312,12 +5317,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5337,7 +5342,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5352,7 +5357,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5362,17 +5367,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5381,11 +5386,16 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5395,12 +5405,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5420,7 +5430,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5435,7 +5445,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5445,17 +5455,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5464,16 +5474,11 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5483,12 +5488,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5508,7 +5513,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5523,7 +5528,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5533,17 +5538,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5552,11 +5557,16 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>10,11,12,13,14,15,16,17,18</t>
+        </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5566,12 +5576,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5591,7 +5601,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5616,17 +5626,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5649,12 +5659,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5674,7 +5684,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5689,7 +5699,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5699,17 +5709,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5718,16 +5728,11 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5737,12 +5742,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5762,7 +5767,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5777,7 +5782,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5787,17 +5792,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5806,11 +5811,16 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5820,12 +5830,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5845,7 +5855,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5860,7 +5870,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5870,17 +5880,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>weibuting</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>魏布婷</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5889,16 +5899,11 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5908,12 +5913,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>weibuting</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>魏布婷</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5933,7 +5938,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5948,7 +5953,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5958,17 +5963,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5977,11 +5982,16 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5991,12 +6001,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6016,7 +6026,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6031,7 +6041,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6041,17 +6051,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>liujianing</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>刘佳宁</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6060,16 +6070,16 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>13,14,15,16</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6079,12 +6089,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>liujianing</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>刘佳宁</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6104,7 +6114,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6119,7 +6129,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6129,17 +6139,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6148,16 +6158,11 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>21,22</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6167,12 +6172,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6192,7 +6197,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6222,12 +6227,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6255,12 +6260,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6280,7 +6285,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6295,7 +6300,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6305,17 +6310,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>lvyixuan</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>吕怡萱</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6328,7 +6333,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6338,12 +6343,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>lvyixuan</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>吕怡萱</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6363,7 +6368,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6378,7 +6383,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6388,17 +6393,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6411,7 +6416,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6421,12 +6426,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6446,7 +6451,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6461,7 +6466,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6471,17 +6476,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6490,16 +6495,16 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>13,14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6509,12 +6514,12 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6534,7 +6539,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6564,12 +6569,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6597,12 +6602,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6622,7 +6627,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6652,12 +6657,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6685,12 +6690,12 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6710,7 +6715,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6725,7 +6730,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6735,17 +6740,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>liujianing</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>刘佳宁</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6763,7 +6768,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -6773,12 +6778,12 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>liujianing</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>刘佳宁</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6798,7 +6803,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6823,17 +6828,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>weibuting</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>魏布婷</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6856,12 +6861,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>weibuting</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>魏布婷</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -6881,7 +6886,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6896,7 +6901,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6906,17 +6911,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>liangxiuzhi</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>梁秀枝</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6925,16 +6930,11 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>liangxiuzhi</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>梁秀枝</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6994,17 +6994,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7077,17 +7077,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7096,16 +7096,11 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -7115,12 +7110,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -7140,7 +7135,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7155,7 +7150,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7165,17 +7160,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>zhuxinlei</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>朱鑫磊</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7193,7 +7188,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -7203,12 +7198,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>zhuxinlei</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>朱鑫磊</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -7228,7 +7223,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7243,7 +7238,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7253,17 +7248,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7281,7 +7276,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -7291,12 +7286,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -7316,7 +7311,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7341,17 +7336,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>jiangmingyang</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>蒋明阳</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7379,12 +7374,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>jiangmingyang</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>蒋明阳</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -7404,7 +7399,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7434,12 +7429,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>fanduo</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>范夺</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7448,11 +7443,11 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7467,12 +7462,12 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>fanduo</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>范夺</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7492,7 +7487,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7517,17 +7512,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7536,7 +7531,12 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7600,17 +7600,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7619,16 +7619,11 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -7638,12 +7633,12 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -7663,7 +7658,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7678,7 +7673,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7688,17 +7683,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7711,7 +7706,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -7721,12 +7716,12 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -7735,6 +7730,94 @@
         </is>
       </c>
       <c r="R84" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>20260911</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>wangxingchen</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>王星晨</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>wangxingchen</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>王星晨</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -7751,7 +7834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7806,10 +7889,10 @@
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="3">
@@ -7832,10 +7915,10 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2142857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -7858,10 +7941,10 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="5">
@@ -7881,13 +7964,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -7910,10 +7993,10 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
@@ -7936,10 +8019,10 @@
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="8">
@@ -7959,13 +8042,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>蒸蒸日上-兴-刘亚雄</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7979,7 +8088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7998,7 +8107,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄初短） 9月9日</t>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄初短） 9月10日</t>
         </is>
       </c>
     </row>
@@ -8079,10 +8188,10 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>11</v>
@@ -8116,10 +8225,10 @@
         <v>11</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>11</v>
@@ -8198,10 +8307,10 @@
         <v>14</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>14</v>
@@ -8239,10 +8348,10 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>11</v>
@@ -8314,16 +8423,16 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>10</v>
@@ -8332,7 +8441,7 @@
         <v>6</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0.6</v>
@@ -8358,10 +8467,10 @@
         <v>10</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>10</v>
@@ -8396,7 +8505,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -8405,7 +8514,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>2</v>
@@ -8414,7 +8523,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0.5</v>
@@ -8440,10 +8549,10 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>11</v>
@@ -8452,13 +8561,13 @@
         <v>8</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>0.7272727272727273</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="13">
@@ -8474,28 +8583,28 @@
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>29</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.6744186046511628</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.7241379310344828</v>
       </c>
     </row>
     <row r="14">
@@ -8515,65 +8624,69 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>5</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>新兵营 汇总</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0.5789473684210527</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>0.4545454545454545</v>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>蒸蒸日上-兴-刘亚雄</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="16">
@@ -8584,33 +8697,70 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>初中 汇总</t>
+          <t>新兵营 汇总</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="5" t="n">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.5686274509803921</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.6551724137931034</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>初中 汇总</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0.6842105263157895</v>
       </c>
     </row>
   </sheetData>
@@ -8627,7 +8777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8690,7 +8840,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8741,7 +8891,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8792,7 +8942,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8843,7 +8993,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8894,7 +9044,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8945,7 +9095,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8996,7 +9146,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9047,7 +9197,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9098,7 +9248,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9149,7 +9299,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -9200,7 +9350,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9251,7 +9401,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9302,7 +9452,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9353,7 +9503,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9404,7 +9554,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9455,7 +9605,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9506,7 +9656,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9557,7 +9707,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9608,7 +9758,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9659,7 +9809,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9710,7 +9860,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9761,7 +9911,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9812,7 +9962,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9863,7 +10013,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9914,7 +10064,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9965,7 +10115,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10016,7 +10166,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -10067,7 +10217,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -10118,7 +10268,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10169,7 +10319,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -10220,7 +10370,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -10271,7 +10421,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -10322,7 +10472,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -10373,7 +10523,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10424,7 +10574,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10475,7 +10625,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10526,7 +10676,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10577,7 +10727,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10628,7 +10778,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10679,7 +10829,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10730,7 +10880,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10781,7 +10931,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -10832,7 +10982,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -10883,7 +11033,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -10934,7 +11084,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -10985,7 +11135,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -11036,7 +11186,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -11087,7 +11237,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -11138,7 +11288,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -11189,7 +11339,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -11240,7 +11390,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -11265,19 +11415,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>wangtao04</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>王涛</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -11291,7 +11441,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -11316,19 +11466,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -11342,7 +11492,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -11367,12 +11517,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -11393,7 +11543,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -11413,24 +11563,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>沐光而行</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -11444,7 +11594,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11469,12 +11619,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -11495,7 +11645,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -11520,12 +11670,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -11546,7 +11696,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -11571,12 +11721,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -11597,7 +11747,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11622,19 +11772,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="H59" t="n">
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -11648,7 +11798,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11673,19 +11823,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="H60" t="n">
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -11699,7 +11849,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11724,16 +11874,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -11750,7 +11900,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11775,19 +11925,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -11801,7 +11951,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11826,12 +11976,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>yanliumeng</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>闫刘梦</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -11852,7 +12002,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -11877,19 +12027,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>yanliumeng</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>闫刘梦</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -11903,7 +12053,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -11928,12 +12078,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -11954,7 +12104,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -11969,26 +12119,26 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -12005,7 +12155,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -12030,19 +12180,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -12056,7 +12206,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -12081,12 +12231,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>caoyumiao</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>曹钰淼</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -12107,7 +12257,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -12132,19 +12282,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>caoyumiao</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>曹钰淼</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -12158,7 +12308,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -12183,16 +12333,16 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>fanduo</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>范夺</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -12209,7 +12359,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -12234,16 +12384,16 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>fanduo</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>范夺</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -12260,7 +12410,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -12285,12 +12435,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -12311,7 +12461,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -12336,12 +12486,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -12362,7 +12512,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -12387,12 +12537,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>liujianing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>刘佳宁</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -12413,7 +12563,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -12438,16 +12588,16 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>liujianing</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>刘佳宁</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -12464,7 +12614,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -12489,16 +12639,16 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -12515,7 +12665,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -12540,12 +12690,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="H77" t="n">
@@ -12566,7 +12716,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -12591,16 +12741,16 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -12617,7 +12767,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -12642,19 +12792,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>weibuting</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>魏布婷</t>
         </is>
       </c>
       <c r="H79" t="n">
         <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -12668,7 +12818,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -12693,19 +12843,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="H80" t="n">
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -12719,7 +12869,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12744,19 +12894,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>weibuting</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>魏布婷</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -12770,7 +12920,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -12795,12 +12945,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -12821,7 +12971,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -12846,12 +12996,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>zhuxinlei</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>朱鑫磊</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -12866,108 +13016,6 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>新兵营-出</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>zhangying04</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>张迎</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>新兵营-出</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>zhuxinlei</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>朱鑫磊</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
         <v>23</v>
       </c>
     </row>
@@ -12982,7 +13030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13172,7 +13220,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
@@ -13181,7 +13229,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H6" t="n">
         <v>0.6</v>
@@ -13236,7 +13284,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -13245,7 +13293,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H8" t="n">
         <v>0.5</v>
@@ -13274,13 +13322,13 @@
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
         <v>0.7272727272727273</v>
       </c>
       <c r="H9" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="10">
@@ -13300,19 +13348,48 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>蒸蒸日上-兴-刘亚雄</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
